--- a/branches/master/ValueSet-mii-vs-icu-code-observation-beatmung-iso11073.xlsx
+++ b/branches/master/ValueSet-mii-vs-icu-code-observation-beatmung-iso11073.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.3</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/master/ValueSet-mii-vs-icu-code-observation-beatmung-iso11073.xlsx
+++ b/branches/master/ValueSet-mii-vs-icu-code-observation-beatmung-iso11073.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="74">
   <si>
     <t>Property</t>
   </si>
@@ -220,6 +220,12 @@
   </si>
   <si>
     <t>End tidal carbon dioxide concentration (or partial pressure) in airway gas</t>
+  </si>
+  <si>
+    <t>151972</t>
+  </si>
+  <si>
+    <t>Airway pressure, primarily during an inspiratory phase</t>
   </si>
   <si>
     <t/>
@@ -492,7 +498,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -672,15 +678,23 @@
         <v>69</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>71</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
